--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134134893</v>
+        <v>137406630</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>87637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>436</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blekspindling agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiostramineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716917</v>
+        <v>716813</v>
       </c>
       <c r="R2" t="n">
-        <v>6368326</v>
+        <v>6368336</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,17 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,30 +765,31 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134893</t>
+          <t>https://artportalen.se/Sighting/137406630</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134134894</v>
+        <v>134134893</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
@@ -832,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716908</v>
+        <v>716917</v>
       </c>
       <c r="R3" t="n">
-        <v>6368321</v>
+        <v>6368326</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre bohål i gran.</t>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,51 +895,56 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134894</t>
+          <t>https://artportalen.se/Sighting/134134893</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134649358</v>
+        <v>134134894</v>
       </c>
       <c r="B4" t="n">
-        <v>43472</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ala Ollajvs övre, Gtl</t>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716991</v>
+        <v>716908</v>
       </c>
       <c r="R4" t="n">
-        <v>6368337</v>
+        <v>6368321</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,22 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre bohål i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,24 +996,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649358</t>
+          <t>https://artportalen.se/Sighting/134134894</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134649362</v>
+        <v>134649358</v>
       </c>
       <c r="B5" t="n">
         <v>43472</v>
@@ -1051,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716963</v>
+        <v>716991</v>
       </c>
       <c r="R5" t="n">
-        <v>6368350</v>
+        <v>6368337</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,13 +1119,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649362</t>
+          <t>https://artportalen.se/Sighting/134649358</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134649364</v>
+        <v>134649362</v>
       </c>
       <c r="B6" t="n">
         <v>43472</v>
@@ -1163,7 +1160,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716921</v>
+        <v>716963</v>
       </c>
       <c r="R6" t="n">
         <v>6368350</v>
@@ -1198,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,13 +1231,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649364</t>
+          <t>https://artportalen.se/Sighting/134649362</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134649367</v>
+        <v>134649364</v>
       </c>
       <c r="B7" t="n">
         <v>43472</v>
@@ -1280,13 +1272,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716913</v>
+        <v>716921</v>
       </c>
       <c r="R7" t="n">
-        <v>6368338</v>
+        <v>6368350</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1356,13 +1348,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649367</t>
+          <t>https://artportalen.se/Sighting/134649364</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134649370</v>
+        <v>134649367</v>
       </c>
       <c r="B8" t="n">
         <v>43472</v>
@@ -1397,13 +1389,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716882</v>
+        <v>716913</v>
       </c>
       <c r="R8" t="n">
-        <v>6368383</v>
+        <v>6368338</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,13 +1465,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649370</t>
+          <t>https://artportalen.se/Sighting/134649367</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134649372</v>
+        <v>134649370</v>
       </c>
       <c r="B9" t="n">
         <v>43472</v>
@@ -1509,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716878</v>
+        <v>716882</v>
       </c>
       <c r="R9" t="n">
-        <v>6368379</v>
+        <v>6368383</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1544,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,13 +1577,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649372</t>
+          <t>https://artportalen.se/Sighting/134649370</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134649374</v>
+        <v>134649372</v>
       </c>
       <c r="B10" t="n">
         <v>43472</v>
@@ -1626,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716855</v>
+        <v>716878</v>
       </c>
       <c r="R10" t="n">
-        <v>6368385</v>
+        <v>6368379</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,12 +1663,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>5 st förökningsyta</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,13 +1694,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649374</t>
+          <t>https://artportalen.se/Sighting/134649372</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134649376</v>
+        <v>134649374</v>
       </c>
       <c r="B11" t="n">
         <v>43472</v>
@@ -1743,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716844</v>
+        <v>716855</v>
       </c>
       <c r="R11" t="n">
-        <v>6368370</v>
+        <v>6368385</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1778,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>3 st, varav 2 i parning?</t>
+          <t>5 st förökningsyta</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,13 +1811,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649376</t>
+          <t>https://artportalen.se/Sighting/134649374</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134649378</v>
+        <v>134649376</v>
       </c>
       <c r="B12" t="n">
         <v>43472</v>
@@ -1860,13 +1852,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716837</v>
+        <v>716844</v>
       </c>
       <c r="R12" t="n">
-        <v>6368407</v>
+        <v>6368370</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,12 +1897,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hotspot minst 10 ex</t>
+          <t>3 st, varav 2 i parning?</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,13 +1928,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649378</t>
+          <t>https://artportalen.se/Sighting/134649376</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134658205</v>
+        <v>134649378</v>
       </c>
       <c r="B13" t="n">
         <v>43472</v>
@@ -1973,17 +1965,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala, Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716886</v>
+        <v>716837</v>
       </c>
       <c r="R13" t="n">
-        <v>6368325</v>
+        <v>6368407</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,12 +2014,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Hotspot minst 10 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,24 +2034,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658205</t>
+          <t>https://artportalen.se/Sighting/134649378</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134658208</v>
+        <v>134658205</v>
       </c>
       <c r="B14" t="n">
         <v>43472</v>
@@ -2094,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716854</v>
+        <v>716886</v>
       </c>
       <c r="R14" t="n">
-        <v>6368341</v>
+        <v>6368325</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2129,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,12 +2131,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,13 +2162,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658208</t>
+          <t>https://artportalen.se/Sighting/134658205</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134658213</v>
+        <v>134658208</v>
       </c>
       <c r="B15" t="n">
         <v>43472</v>
@@ -2211,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716823</v>
+        <v>716854</v>
       </c>
       <c r="R15" t="n">
-        <v>6368339</v>
+        <v>6368341</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2246,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,12 +2248,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,13 +2279,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658213</t>
+          <t>https://artportalen.se/Sighting/134658208</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134658216</v>
+        <v>134658213</v>
       </c>
       <c r="B16" t="n">
         <v>43472</v>
@@ -2328,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716812</v>
+        <v>716823</v>
       </c>
       <c r="R16" t="n">
-        <v>6368330</v>
+        <v>6368339</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2363,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2404,13 +2396,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658216</t>
+          <t>https://artportalen.se/Sighting/134658213</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134658217</v>
+        <v>134658216</v>
       </c>
       <c r="B17" t="n">
         <v>43472</v>
@@ -2445,10 +2437,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716816</v>
+        <v>716812</v>
       </c>
       <c r="R17" t="n">
-        <v>6368325</v>
+        <v>6368330</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2480,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2490,12 +2482,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,13 +2513,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658217</t>
+          <t>https://artportalen.se/Sighting/134658216</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134658219</v>
+        <v>134658217</v>
       </c>
       <c r="B18" t="n">
         <v>43472</v>
@@ -2562,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716797</v>
+        <v>716816</v>
       </c>
       <c r="R18" t="n">
-        <v>6368329</v>
+        <v>6368325</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2597,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2638,13 +2630,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658219</t>
+          <t>https://artportalen.se/Sighting/134658217</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134658220</v>
+        <v>134658219</v>
       </c>
       <c r="B19" t="n">
         <v>43472</v>
@@ -2679,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716825</v>
+        <v>716797</v>
       </c>
       <c r="R19" t="n">
-        <v>6368358</v>
+        <v>6368329</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2714,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2724,12 +2716,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,13 +2747,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658220</t>
+          <t>https://artportalen.se/Sighting/134658219</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134658222</v>
+        <v>134658220</v>
       </c>
       <c r="B20" t="n">
         <v>43472</v>
@@ -2796,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716846</v>
+        <v>716825</v>
       </c>
       <c r="R20" t="n">
-        <v>6368363</v>
+        <v>6368358</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2831,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2833,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,16 +2864,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658222</t>
+          <t>https://artportalen.se/Sighting/134658220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134134868</v>
+        <v>134658222</v>
       </c>
       <c r="B21" t="n">
-        <v>43469</v>
+        <v>43472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2889,53 +2881,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201116</v>
+        <v>101242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716951</v>
+        <v>716846</v>
       </c>
       <c r="R21" t="n">
-        <v>6368356</v>
+        <v>6368363</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2962,12 +2935,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,68 +2966,73 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134868</t>
+          <t>https://artportalen.se/Sighting/134658222</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134134747</v>
+        <v>134134868</v>
       </c>
       <c r="B22" t="n">
-        <v>99218</v>
+        <v>43469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219862</v>
+        <v>201116</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3048,10 +3041,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716928</v>
+        <v>716951</v>
       </c>
       <c r="R22" t="n">
-        <v>6368363</v>
+        <v>6368356</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3086,11 +3079,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3102,7 +3090,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3119,13 +3107,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134747</t>
+          <t>https://artportalen.se/Sighting/134134868</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134751</v>
+        <v>134134747</v>
       </c>
       <c r="B23" t="n">
         <v>99218</v>
@@ -3155,7 +3143,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3169,10 +3157,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716919</v>
+        <v>716928</v>
       </c>
       <c r="R23" t="n">
-        <v>6368337</v>
+        <v>6368363</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3207,6 +3195,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Även 5 fjolårsstänglar.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3235,16 +3228,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134751</t>
+          <t>https://artportalen.se/Sighting/134134747</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134723</v>
+        <v>134134751</v>
       </c>
       <c r="B24" t="n">
-        <v>99224</v>
+        <v>99218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,26 +3245,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3285,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716841</v>
+        <v>716919</v>
       </c>
       <c r="R24" t="n">
-        <v>6368309</v>
+        <v>6368337</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3351,13 +3344,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134723</t>
+          <t>https://artportalen.se/Sighting/134134751</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134134742</v>
+        <v>134134723</v>
       </c>
       <c r="B25" t="n">
         <v>99224</v>
@@ -3387,7 +3380,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3401,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716930</v>
+        <v>716841</v>
       </c>
       <c r="R25" t="n">
-        <v>6368372</v>
+        <v>6368309</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3467,13 +3460,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134742</t>
+          <t>https://artportalen.se/Sighting/134134723</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134775</v>
+        <v>134134742</v>
       </c>
       <c r="B26" t="n">
         <v>99224</v>
@@ -3503,7 +3496,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3517,10 +3510,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716872</v>
+        <v>716930</v>
       </c>
       <c r="R26" t="n">
-        <v>6368325</v>
+        <v>6368372</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3583,13 +3576,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134775</t>
+          <t>https://artportalen.se/Sighting/134134742</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134778</v>
+        <v>134134775</v>
       </c>
       <c r="B27" t="n">
         <v>99224</v>
@@ -3619,7 +3612,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3633,10 +3626,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716866</v>
+        <v>716872</v>
       </c>
       <c r="R27" t="n">
-        <v>6368338</v>
+        <v>6368325</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3699,13 +3692,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134778</t>
+          <t>https://artportalen.se/Sighting/134134775</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134134780</v>
+        <v>134134778</v>
       </c>
       <c r="B28" t="n">
         <v>99224</v>
@@ -3735,7 +3728,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3749,10 +3742,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716862</v>
+        <v>716866</v>
       </c>
       <c r="R28" t="n">
-        <v>6368351</v>
+        <v>6368338</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3815,13 +3808,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134780</t>
+          <t>https://artportalen.se/Sighting/134134778</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134134791</v>
+        <v>134134780</v>
       </c>
       <c r="B29" t="n">
         <v>99224</v>
@@ -3851,7 +3844,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3865,10 +3858,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716813</v>
+        <v>716862</v>
       </c>
       <c r="R29" t="n">
-        <v>6368335</v>
+        <v>6368351</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3931,13 +3924,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134791</t>
+          <t>https://artportalen.se/Sighting/134134780</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134134794</v>
+        <v>134134791</v>
       </c>
       <c r="B30" t="n">
         <v>99224</v>
@@ -3981,10 +3974,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716821</v>
+        <v>716813</v>
       </c>
       <c r="R30" t="n">
-        <v>6368327</v>
+        <v>6368335</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4047,33 +4040,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134794</t>
+          <t>https://artportalen.se/Sighting/134134791</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134134727</v>
+        <v>134134794</v>
       </c>
       <c r="B31" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4081,17 +4074,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716881</v>
+        <v>716821</v>
       </c>
       <c r="R31" t="n">
-        <v>6368310</v>
+        <v>6368327</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4154,13 +4156,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134727</t>
+          <t>https://artportalen.se/Sighting/134134794</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134134729</v>
+        <v>134134727</v>
       </c>
       <c r="B32" t="n">
         <v>110159</v>
@@ -4195,10 +4197,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>716894</v>
+        <v>716881</v>
       </c>
       <c r="R32" t="n">
-        <v>6368308</v>
+        <v>6368310</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4261,13 +4263,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134729</t>
+          <t>https://artportalen.se/Sighting/134134727</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134134740</v>
+        <v>134134729</v>
       </c>
       <c r="B33" t="n">
         <v>110159</v>
@@ -4302,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>716946</v>
+        <v>716894</v>
       </c>
       <c r="R33" t="n">
-        <v>6368368</v>
+        <v>6368308</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4340,11 +4342,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>AVA gräns 10 m O.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4373,13 +4370,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134740</t>
+          <t>https://artportalen.se/Sighting/134134729</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134134743</v>
+        <v>134134740</v>
       </c>
       <c r="B34" t="n">
         <v>110159</v>
@@ -4414,10 +4411,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>716930</v>
+        <v>716946</v>
       </c>
       <c r="R34" t="n">
-        <v>6368372</v>
+        <v>6368368</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4452,6 +4449,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>AVA gräns 10 m O.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4480,13 +4482,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134743</t>
+          <t>https://artportalen.se/Sighting/134134740</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134134745</v>
+        <v>134134743</v>
       </c>
       <c r="B35" t="n">
         <v>110159</v>
@@ -4521,10 +4523,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>716928</v>
+        <v>716930</v>
       </c>
       <c r="R35" t="n">
-        <v>6368363</v>
+        <v>6368372</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4587,13 +4589,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134745</t>
+          <t>https://artportalen.se/Sighting/134134743</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134134748</v>
+        <v>134134745</v>
       </c>
       <c r="B36" t="n">
         <v>110159</v>
@@ -4628,10 +4630,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>716919</v>
+        <v>716928</v>
       </c>
       <c r="R36" t="n">
-        <v>6368359</v>
+        <v>6368363</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4694,13 +4696,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134748</t>
+          <t>https://artportalen.se/Sighting/134134745</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134134753</v>
+        <v>134134748</v>
       </c>
       <c r="B37" t="n">
         <v>110159</v>
@@ -4738,7 +4740,7 @@
         <v>716919</v>
       </c>
       <c r="R37" t="n">
-        <v>6368337</v>
+        <v>6368359</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4801,13 +4803,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134753</t>
+          <t>https://artportalen.se/Sighting/134134748</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134134755</v>
+        <v>134134753</v>
       </c>
       <c r="B38" t="n">
         <v>110159</v>
@@ -4842,10 +4844,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716917</v>
+        <v>716919</v>
       </c>
       <c r="R38" t="n">
-        <v>6368326</v>
+        <v>6368337</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4908,13 +4910,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134755</t>
+          <t>https://artportalen.se/Sighting/134134753</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134134761</v>
+        <v>134134755</v>
       </c>
       <c r="B39" t="n">
         <v>110159</v>
@@ -4949,10 +4951,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>716908</v>
+        <v>716917</v>
       </c>
       <c r="R39" t="n">
-        <v>6368321</v>
+        <v>6368326</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5015,13 +5017,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134761</t>
+          <t>https://artportalen.se/Sighting/134134755</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134134763</v>
+        <v>134134761</v>
       </c>
       <c r="B40" t="n">
         <v>110159</v>
@@ -5056,10 +5058,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716899</v>
+        <v>716908</v>
       </c>
       <c r="R40" t="n">
-        <v>6368322</v>
+        <v>6368321</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5122,13 +5124,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134763</t>
+          <t>https://artportalen.se/Sighting/134134761</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134134765</v>
+        <v>134134763</v>
       </c>
       <c r="B41" t="n">
         <v>110159</v>
@@ -5163,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716892</v>
+        <v>716899</v>
       </c>
       <c r="R41" t="n">
-        <v>6368329</v>
+        <v>6368322</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5229,13 +5231,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134765</t>
+          <t>https://artportalen.se/Sighting/134134763</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134134767</v>
+        <v>134134765</v>
       </c>
       <c r="B42" t="n">
         <v>110159</v>
@@ -5270,10 +5272,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716880</v>
+        <v>716892</v>
       </c>
       <c r="R42" t="n">
-        <v>6368316</v>
+        <v>6368329</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5336,13 +5338,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134767</t>
+          <t>https://artportalen.se/Sighting/134134765</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134134769</v>
+        <v>134134767</v>
       </c>
       <c r="B43" t="n">
         <v>110159</v>
@@ -5377,10 +5379,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716876</v>
+        <v>716880</v>
       </c>
       <c r="R43" t="n">
-        <v>6368320</v>
+        <v>6368316</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5443,13 +5445,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134769</t>
+          <t>https://artportalen.se/Sighting/134134767</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134134773</v>
+        <v>134134769</v>
       </c>
       <c r="B44" t="n">
         <v>110159</v>
@@ -5484,10 +5486,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716872</v>
+        <v>716876</v>
       </c>
       <c r="R44" t="n">
-        <v>6368325</v>
+        <v>6368320</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5550,13 +5552,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134773</t>
+          <t>https://artportalen.se/Sighting/134134769</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134134776</v>
+        <v>134134773</v>
       </c>
       <c r="B45" t="n">
         <v>110159</v>
@@ -5591,10 +5593,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716866</v>
+        <v>716872</v>
       </c>
       <c r="R45" t="n">
-        <v>6368338</v>
+        <v>6368325</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5657,13 +5659,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134776</t>
+          <t>https://artportalen.se/Sighting/134134773</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134134782</v>
+        <v>134134776</v>
       </c>
       <c r="B46" t="n">
         <v>110159</v>
@@ -5698,10 +5700,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716867</v>
+        <v>716866</v>
       </c>
       <c r="R46" t="n">
-        <v>6368358</v>
+        <v>6368338</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5764,13 +5766,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134782</t>
+          <t>https://artportalen.se/Sighting/134134776</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134134786</v>
+        <v>134134782</v>
       </c>
       <c r="B47" t="n">
         <v>110159</v>
@@ -5805,13 +5807,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716848</v>
+        <v>716867</v>
       </c>
       <c r="R47" t="n">
-        <v>6368363</v>
+        <v>6368358</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5843,11 +5845,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5859,7 +5856,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5876,13 +5873,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134786</t>
+          <t>https://artportalen.se/Sighting/134134782</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134134789</v>
+        <v>134134786</v>
       </c>
       <c r="B48" t="n">
         <v>110159</v>
@@ -5917,13 +5914,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>716826</v>
+        <v>716848</v>
       </c>
       <c r="R48" t="n">
-        <v>6368340</v>
+        <v>6368363</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5957,7 +5954,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd. 40 m S skiftesgräns.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5971,7 +5968,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5988,13 +5985,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134789</t>
+          <t>https://artportalen.se/Sighting/134134786</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134134792</v>
+        <v>134134789</v>
       </c>
       <c r="B49" t="n">
         <v>110159</v>
@@ -6029,10 +6026,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>716813</v>
+        <v>716826</v>
       </c>
       <c r="R49" t="n">
-        <v>6368335</v>
+        <v>6368340</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6069,7 +6066,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>AVA slut 20 m V.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6100,13 +6097,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134792</t>
+          <t>https://artportalen.se/Sighting/134134789</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134134795</v>
+        <v>134134792</v>
       </c>
       <c r="B50" t="n">
         <v>110159</v>
@@ -6141,10 +6138,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716821</v>
+        <v>716813</v>
       </c>
       <c r="R50" t="n">
-        <v>6368327</v>
+        <v>6368335</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6179,6 +6176,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>AVA slut 20 m V.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6207,33 +6209,33 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134795</t>
+          <t>https://artportalen.se/Sighting/134134792</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134134781</v>
+        <v>134134795</v>
       </c>
       <c r="B51" t="n">
-        <v>103907</v>
+        <v>110159</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223284</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6248,10 +6250,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>716867</v>
+        <v>716821</v>
       </c>
       <c r="R51" t="n">
-        <v>6368358</v>
+        <v>6368327</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6286,11 +6288,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>10 cm i diameter, kapad!</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6319,7 +6316,232 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134134795</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134134781</v>
+      </c>
+      <c r="B52" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>716867</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6368358</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>10 cm i diameter, kapad!</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134134781</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137406632</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ala, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>716835</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6368382</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137406632</t>
         </is>
       </c>
     </row>
@@ -6375,6 +6597,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406630</v>
       </c>
       <c r="B2" t="n">
-        <v>87637</v>
+        <v>87648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>137406632</v>
       </c>
       <c r="B53" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406630</v>
       </c>
       <c r="B2" t="n">
-        <v>87648</v>
+        <v>87649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>137406632</v>
       </c>
       <c r="B53" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406630</v>
       </c>
       <c r="B2" t="n">
-        <v>87649</v>
+        <v>87652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>137406632</v>
       </c>
       <c r="B53" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406630</v>
       </c>
       <c r="B2" t="n">
-        <v>87652</v>
+        <v>87656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>137406632</v>
       </c>
       <c r="B53" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
